--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.40.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.40.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.40.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.40.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -597,19 +597,23 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: lowing cases have been decided:â€” Of the</t>
+          <t>L20: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]THE APPEARANCE.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]THE APPEARANCE.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L25: isolated marker/symbol line :: 33</t>
+          <t>L20: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
@@ -645,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -654,26 +658,22 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L37: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: the subpa Ã¦ ena must be made, under the Order as t</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: think fits.â€�.</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L47: symbol-only separator/garbage line :: 130.)</t>
+          <t>L25: isolated marker/symbol line :: 33</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -710,16 +710,12 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: lowing cases have been decided â€”Of the six days,</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: C</t>
+          <t>L47: symbol-only separator/garbage line :: 130.)</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -746,12 +742,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -764,7 +760,11 @@
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
-      <c r="N5" s="1" t="inlineStr"/>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>L55: isolated marker/symbol line :: C</t>
+        </is>
+      </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
           <t>L84: isolated marker/symbol line :: C</t>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
